--- a/Result/profitability/5601.xlsx
+++ b/Result/profitability/5601.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.09625</v>
+        <v>0.095</v>
       </c>
       <c r="N2" t="n">
-        <v>60.45375</v>
+        <v>60.62</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.06</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09</v>
+        <v>0.09375</v>
       </c>
       <c r="N3" t="n">
-        <v>61.51125</v>
+        <v>61.54625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -902,7 +902,7 @@
         <v>0.08875000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>62.55</v>
+        <v>62.74625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.06</v>
       </c>
       <c r="M5" t="n">
-        <v>0.08375</v>
+        <v>0.0825</v>
       </c>
       <c r="N5" t="n">
-        <v>62.93</v>
+        <v>62.825</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07875000000000001</v>
+        <v>0.0775</v>
       </c>
       <c r="N6" t="n">
-        <v>63.48999999999999</v>
+        <v>63.39</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1267,7 +1267,7 @@
         <v>0.0725</v>
       </c>
       <c r="N7" t="n">
-        <v>63.85</v>
+        <v>63.94</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>0.0675</v>
       </c>
       <c r="N8" t="n">
-        <v>64.58</v>
+        <v>64.57875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5601</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>24</v>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="n">
+        <v>14</v>
+      </c>
+      <c r="F75" t="n">
+        <v>60.09</v>
+      </c>
+      <c r="G75" t="n">
+        <v>8</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>33.53%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>8</v>
+      </c>
+      <c r="K75" t="n">
+        <v>7</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.09999999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>59.80875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.00999999999999801</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0001663893510814862</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.009999999999999995</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.09090909090909083</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.8399999999999963</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.01378631216149673</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
